--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -461,16 +456,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
-  usa </t>
+          <t>K4FYmLD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>K4FYmLD</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>EgT3xN3</t>
         </is>
@@ -487,16 +476,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
+          <t>022mBmS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>022mBmS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>UL7r7du</t>
         </is>
@@ -513,16 +496,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
+          <t>022mBmS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>022mBmS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>86yPt28</t>
         </is>
@@ -539,16 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
+          <t>6BusaLE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>6BusaLE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>zoZ995a</t>
         </is>
@@ -565,16 +536,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
-  usa </t>
+          <t>xA45kov</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>EgT3xN3</t>
         </is>
@@ -591,16 +556,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pekmic i 
-  usa </t>
+          <t>Onn3tCA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>6gpXy3v</t>
         </is>
@@ -617,16 +576,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
+          <t>lAVQ9RG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>lAVQ9RG</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>UL7r7du</t>
         </is>
@@ -643,16 +596,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t>WWvwigh</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>UFWZoX9</t>
         </is>
@@ -669,16 +616,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t>l6eEjGl</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>l6eEjGl</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>UFWZoX9</t>
         </is>
@@ -695,16 +636,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t>2PIEeC7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>2PIEeC7</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>rXawJi8</t>
         </is>
@@ -721,18 +656,52 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
+          <t>WWvwigh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>KtuTuMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,47 +453,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>K4FYmLD</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>6gpXy3v</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rXawJi8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>022mBmS</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tOpyQa2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,90 +503,100 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t xml:space="preserve">simon n 
+  usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>86yPt28</t>
+          <t>roEEsq7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sd7snoa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6BusaLE</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>022mBmS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Uw6sTk0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6gpXy3v</t>
+          <t>roEEsq7</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>lAVQ9RG</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>UL7r7du</t>
         </is>
@@ -588,120 +605,147 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UFWZoX9</t>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>l6eEjGl</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2PIEeC7</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rXawJi8</t>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rJ9D8rz</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KtuTuMN</t>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2PIEeC7</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>KtuTuMN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Onn3tCA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sd7snoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,6 +749,708 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GzULyFo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KtuTuMN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>lAVQ9RG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Uw6sTk0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GzULyFo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>lAVQ9RG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6gpXy3v</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>022mBmS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>rJ9D8rz</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GzULyFo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sd7snoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>tOpyQa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>rXawJi8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,708 +749,6 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>jqf7smJ3</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2PIEeC7</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>K4zRMgT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>G0IRHiWk</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">penso c 
-  usa </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>nJ01AhX</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>EgT3xN3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fiHVGBod</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>K4FYmLD</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>6BusaLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4nbBt7Y9</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>GzULyFo</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>zoZ995a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>b9cFuRmG</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>K4FYmLD</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>l6eEjGl</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zZKrObIr</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>6BusaLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hAFmNIXl</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>86yPt28</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>K4zRMgT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>QNDeLd21</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>zoZ995a</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>W0EiMxme</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>jBBpU7Y</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>UL7r7du</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>xbHaKGH7</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gonzales g 
-  usa </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>KtuTuMN</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>lAVQ9RG</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>v3erq0f8</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">demianchuk s 
-  usa </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>IgfnrK9E</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>dp6AQn9</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>nTbjsvPK</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>86yPt28</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Uw6sTk0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>YyTMIXGq</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gonzales g 
-  usa </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>GzULyFo</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>lAVQ9RG</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">penso c 
-  usa </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>6gpXy3v</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>EgT3xN3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>022mBmS</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>zoZ995a</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>nJ01AhX</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>6BusaLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2PIEeC7</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>rJ9D8rz</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>K4zRMgT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>GzULyFo</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>l6eEjGl</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>6BusaLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>jBBpU7Y</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>tOpyQa2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>rXawJi8</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2PIEeC7</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>UL7r7du</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -456,20 +451,9 @@
           <t>z7pPU9Zc</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6gpXy3v</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>rXawJi8</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -477,20 +461,9 @@
           <t>EcqTTTl4</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>nJ01AhX</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>tOpyQa2</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -498,25 +471,9 @@
           <t>tpoLVkKi</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>roEEsq7</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -524,20 +481,9 @@
           <t>ln2oxMH4</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>K4FYmLD</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>EgT3xN3</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -545,20 +491,9 @@
           <t>WYwYSm4A</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>022mBmS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Uw6sTk0</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -566,20 +501,9 @@
           <t>APxxS7JG</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>roEEsq7</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>K4zRMgT</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -590,13 +514,12 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>UL7r7du</t>
         </is>
@@ -611,13 +534,12 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>dp6AQn9</t>
         </is>
@@ -632,120 +554,14 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>l6eEjGl</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>rJ9D8rz</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jBBpU7Y</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>dp6AQn9</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>KtuTuMN</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>86yPt28</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,120 +448,60 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>KtuTuMN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sd7snoa</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4nxtRRYM</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>UL7r7du</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>IktpQolT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>dp6AQn9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OWICL5dp</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>l6eEjGl</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,23 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>copiado_avoid_nan</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
         </is>
       </c>
     </row>
@@ -451,19 +441,7 @@
           <t>UT5bq9li</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>KtuTuMN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -471,19 +449,7 @@
           <t>Ma0gz0nH</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -491,19 +457,7 @@
           <t>8K42rT3c</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>86yPt28</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,30 +434,1087 @@
           <t>copiado_avoid_nan</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,708 +814,6 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>zoZ995a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>nJ01AhXP</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>EgT3xN3S</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>K4FYmLD9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Uw6sTk0t</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>UFWZoX9L</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>z9ZXDy6o</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Onn3tCA5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>lAVQ9RGh</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Onn3tCA5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>xlCTyDNL</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>lAVQ9RGh</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>rRCPxg8F</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>z9yhkyHs</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>zoZ995a</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>4rtdleWm</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>rZv0mFof</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>QcU4nZ00</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>UFWZoX9L</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>xYX8ogG6</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>WfXCpDVC</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>AoWGqXpJ</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>nJ01AhXP</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Onn3tCA5</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>n3Fa8GNJ</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>rZ0V2fos</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>lAVQ9RGh</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>dx5Z1E0m</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>KtuTuMN0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>v1fv1YFg</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>EqKWmJfM</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>QgE37zwQ</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Uw6sTk0t</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -453,49 +453,59 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6gpXy3v</t>
+          <t>EgT3xN3S</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rXawJi8</t>
+          <t>Uw6sTk0t</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nJ01AhX</t>
+          <t>z9ZXDy6o</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tOpyQa2</t>
+          <t>xA45kovo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -503,249 +513,304 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>roEEsq7</t>
+          <t>lAVQ9RGh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sd7snoa</t>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>K4FYmLD</t>
+          <t>roEEsq76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uw6sTk0</t>
+          <t>86yPt28f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>roEEsq7</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>K4zRMgT</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
+          <t>nJ01AhXP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>xA45kov</t>
+          <t>EgT3xN3S</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>dp6AQn9</t>
+          <t>zoZ995a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>z9ZXDy6</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>l6eEjGl</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>z9ZXDy6</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>rJ9D8rz</t>
+          <t>K4FYmLD9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>jBBpU7Y</t>
+          <t>EqKWmJfM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>dp6AQn9</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KtuTuMN</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EqKWmJf</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Onn3tCA</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sd7snoa</t>
+          <t>Uw6sTk0t</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>86yPt28</t>
+          <t>EqKWmJfM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UFWZoX9</t>
+          <t>l6eEjGlO</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,7 +654,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>zoZ995af</t>
         </is>
       </c>
     </row>
@@ -811,6 +811,812 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">surgan j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MRdhQQTs</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corbyn m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>EgT3xN3S</t>
@@ -485,12 +480,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>z9ZXDy6o</t>
@@ -511,12 +501,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>lAVQ9RGh</t>
@@ -537,12 +522,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>roEEsq76</t>
@@ -563,12 +543,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>rJ9D8rzj</t>
@@ -589,12 +564,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>tOpyQa24</t>
@@ -615,12 +585,7 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>nJ01AhXP</t>
@@ -641,12 +606,7 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>EgT3xN3S</t>
@@ -667,12 +627,7 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>zoZ995af</t>
@@ -693,12 +648,7 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>UL7r7duf</t>
@@ -719,12 +669,7 @@
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>EqKWmJfM</t>
@@ -745,12 +690,7 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>UL7r7duf</t>
@@ -771,12 +711,7 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>tOpyQa24</t>
@@ -797,12 +732,7 @@
       <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>EqKWmJfM</t>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>K4FYmLD9</t>
+          <t xml:space="preserve">rivas v 
+  usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>txm4BKVR</t>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>K4zRMgTN</t>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EgT3xN3S</t>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,19 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t xml:space="preserve">szpala l 
+  usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -576,19 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bFuhdIb3</t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dp6AQn9c</t>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -596,19 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t xml:space="preserve">rivas v 
+  usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -616,19 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t xml:space="preserve">simon n 
+  usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -636,19 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t xml:space="preserve">da silva a 
+  usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -656,19 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t xml:space="preserve">gonzalez g  jr 
+  usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,19 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CfE5JcGF</t>
+          <t xml:space="preserve">gonzalez g  jr 
+  usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>l6eEjGlO</t>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -696,19 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t xml:space="preserve">simon n 
+  usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -716,12 +799,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bFuhdIb3</t>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/usa/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -456,25 +451,9 @@
           <t>AszX60rp</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -482,25 +461,9 @@
           <t>jix3jCxF</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -508,25 +471,9 @@
           <t>h6Py6Kcj</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>6gpXy3vi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -534,25 +481,9 @@
           <t>WdOu5vDd</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villarreal a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>KtuTuMN0</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -560,25 +491,9 @@
           <t>KCHNTNkc</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -586,25 +501,9 @@
           <t>b3GRSs53</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>EgT3xN3S</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -612,25 +511,9 @@
           <t>tS5WR1K9</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -643,16 +526,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>022mBmSn</t>
         </is>
@@ -669,16 +546,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>UFWZoX9L</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>86yPt28f</t>
         </is>
@@ -695,16 +566,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>WSL0wFD4</t>
         </is>
@@ -721,16 +586,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
-  usa </t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
         <is>
           <t>rXawJi8t</t>
         </is>
@@ -747,16 +606,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
-  usa </t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t>rXawJi8t</t>
         </is>
@@ -773,16 +626,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>86yPt28f</t>
         </is>
@@ -799,16 +646,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
-        <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
         <is>
           <t>rXawJi8t</t>
         </is>
